--- a/design_issues/codescene/Summary.xlsx
+++ b/design_issues/codescene/Summary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\diagrams\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Project</t>
   </si>
@@ -42,12 +42,6 @@
     <t>Complex Conditional</t>
   </si>
   <si>
-    <t>Lines of Code in a Single File</t>
-  </si>
-  <si>
-    <t>Overall Function Size</t>
-  </si>
-  <si>
     <t>Excess Number of Function Arguments</t>
   </si>
   <si>
@@ -57,24 +51,6 @@
     <t>Primitive Obsession</t>
   </si>
   <si>
-    <t>String Heavy Function Arguments</t>
-  </si>
-  <si>
-    <t>Deep, Nested Complexity</t>
-  </si>
-  <si>
-    <t>Low Cohesion</t>
-  </si>
-  <si>
-    <t>Lines of Declarations in a Single File</t>
-  </si>
-  <si>
-    <t>Global Conditionals</t>
-  </si>
-  <si>
-    <t>Deep, Global Nested Complexity</t>
-  </si>
-  <si>
     <t>P1_CVBuilder</t>
   </si>
   <si>
@@ -106,6 +82,12 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Deep Nested Complexity</t>
   </si>
 </sst>
 </file>
@@ -169,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -178,6 +160,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -482,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.36328125" style="2" customWidth="1"/>
@@ -492,22 +477,15 @@
     <col min="5" max="5" width="19.08984375" style="2" customWidth="1"/>
     <col min="6" max="6" width="22.26953125" style="2" customWidth="1"/>
     <col min="7" max="7" width="31.08984375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.6328125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.26953125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.1796875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="26.54296875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="33.54296875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="27.7265625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="20.7265625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="37.1796875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="23.6328125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="28.453125" style="2" customWidth="1"/>
-    <col min="19" max="19" width="17.26953125" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="8.7265625" style="2"/>
+    <col min="8" max="8" width="35.26953125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.1796875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.54296875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.7265625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.26953125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,36 +517,19 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="B2" s="2">
-        <v>226</v>
+        <f>SUM(C2:L2)</f>
+        <v>217</v>
       </c>
       <c r="C2" s="2">
         <v>64</v>
@@ -586,45 +547,28 @@
         <v>30</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K2" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>6</v>
-      </c>
-      <c r="M2" s="2">
-        <v>9</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
-        <v>102</v>
+        <f t="shared" ref="B3:B11" si="0">SUM(C3:L3)</f>
+        <v>90</v>
       </c>
       <c r="C3" s="2">
         <v>35</v>
@@ -642,45 +586,28 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K3" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="2">
-        <v>7</v>
-      </c>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="B4" s="2">
-        <v>133</v>
+        <f t="shared" si="0"/>
+        <v>113</v>
       </c>
       <c r="C4" s="2">
         <v>44</v>
@@ -698,44 +625,27 @@
         <v>5</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K4" s="2">
         <v>0</v>
       </c>
       <c r="L4" s="2">
-        <v>23</v>
-      </c>
-      <c r="M4" s="2">
-        <v>11</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C5" s="2">
@@ -768,31 +678,14 @@
       <c r="L5" s="2">
         <v>0</v>
       </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>63</v>
+        <f t="shared" si="0"/>
+        <v>62</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
@@ -810,44 +703,27 @@
         <v>5</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>2</v>
+      </c>
+      <c r="L6" s="2">
         <v>1</v>
       </c>
-      <c r="K6" s="2">
-        <v>10</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2</v>
-      </c>
-      <c r="M6" s="2">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2">
-        <v>2</v>
-      </c>
-      <c r="O6" s="2">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2">
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="C7" s="2">
@@ -869,41 +745,24 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
       <c r="K7" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2">
-        <v>5</v>
-      </c>
-      <c r="O7" s="2">
         <v>2</v>
       </c>
-      <c r="P7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
+        <f t="shared" si="0"/>
         <v>116</v>
       </c>
       <c r="C8" s="2">
@@ -925,42 +784,25 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
       </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B9" s="2">
-        <v>169</v>
+        <f t="shared" si="0"/>
+        <v>168</v>
       </c>
       <c r="C9" s="2">
         <v>53</v>
@@ -978,45 +820,28 @@
         <v>12</v>
       </c>
       <c r="H9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J9" s="2">
+        <v>6</v>
+      </c>
+      <c r="K9" s="2">
         <v>1</v>
       </c>
-      <c r="K9" s="2">
-        <v>14</v>
-      </c>
       <c r="L9" s="2">
-        <v>6</v>
-      </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2">
-        <v>1</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>199</v>
       </c>
       <c r="C10" s="2">
         <v>78</v>
@@ -1034,45 +859,28 @@
         <v>27</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K10" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2">
-        <v>8</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B11" s="2">
-        <v>192</v>
+        <f t="shared" si="0"/>
+        <v>191</v>
       </c>
       <c r="C11" s="2">
         <v>47</v>
@@ -1087,96 +895,71 @@
         <v>23</v>
       </c>
       <c r="G11" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J11" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2">
-        <v>3</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2">
-        <v>5</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>1</v>
-      </c>
-      <c r="R11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>1350</v>
+        <f>SUM(B2:B11)</f>
+        <v>1305</v>
       </c>
       <c r="C12" s="3">
+        <f>SUM(C2:C11)</f>
         <v>383</v>
       </c>
       <c r="D12" s="3">
+        <f t="shared" ref="D12:E12" si="1">SUM(D2:D11)</f>
         <v>76</v>
       </c>
       <c r="E12" s="3">
+        <f t="shared" si="1"/>
         <v>377</v>
       </c>
       <c r="F12" s="3">
+        <f t="shared" ref="F12:G12" si="2">SUM(F2:F11)</f>
         <v>171</v>
       </c>
       <c r="G12" s="3">
-        <v>111</v>
+        <f t="shared" si="2"/>
+        <v>112</v>
       </c>
       <c r="H12" s="3">
-        <v>2</v>
+        <f t="shared" ref="H12" si="3">SUM(H2:H11)</f>
+        <v>23</v>
       </c>
       <c r="I12" s="3">
-        <v>3</v>
+        <f t="shared" ref="I12" si="4">SUM(I2:I11)</f>
+        <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>23</v>
+        <f t="shared" ref="J12" si="5">SUM(J2:J11)</f>
+        <v>60</v>
       </c>
       <c r="K12" s="3">
-        <v>79</v>
+        <f t="shared" ref="K12" si="6">SUM(K2:K11)</f>
+        <v>15</v>
       </c>
       <c r="L12" s="3">
-        <v>60</v>
-      </c>
-      <c r="M12" s="3">
-        <v>31</v>
-      </c>
-      <c r="N12" s="3">
-        <v>14</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1</v>
-      </c>
-      <c r="R12" s="3">
-        <v>1</v>
+        <f t="shared" ref="L12" si="7">SUM(L2:L11)</f>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
